--- a/nino/Insight_Rotiseria_Panaderia_NINO.xlsx
+++ b/nino/Insight_Rotiseria_Panaderia_NINO.xlsx
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Datos: 16/02/2026 - 18/03/2026 (31 dias) | Estructura de costos + Cross-selling | Marzo 2026</t>
+          <t xml:space="preserve">  Datos: 01/03/2026 - 31/03/2026 (31 dias) | Estructura de costos + Cross-selling | Marzo 2026</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1137</v>
+        <v>1167</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>9795</v>
+        <v>9158</v>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr"/>
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>11155381</v>
+        <v>10376216</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>27691383</v>
+        <v>20503352</v>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr"/>
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>53251462</v>
+        <v>50609522</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>349130958</v>
+        <v>312503751</v>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
       <c r="E18" s="12" t="inlineStr"/>
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>4.8x</t>
+          <t>4.9x</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>12.6x</t>
+          <t>15.2x</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>56637</v>
+        <v>52275</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>38470</v>
+        <v>36361</v>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr"/>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>27606</v>
+        <v>25303</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>27606</v>
+        <v>25303</v>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr"/>
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>29031</v>
+        <v>26972</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>10864</v>
+        <v>11058</v>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Rotis: +$29,031 | Panad: +$10,864 por ticket</t>
+          <t>Rotis: +$26,972 | Panad: +$11,058 por ticket</t>
         </is>
       </c>
     </row>
@@ -937,15 +937,15 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>32717190</v>
+        <v>29921556</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="F28" s="16" t="n">
-        <v>1635860</v>
+        <v>1496078</v>
       </c>
     </row>
     <row r="29">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>16891360</v>
+        <v>17455090</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="F29" s="16" t="n">
-        <v>2533704</v>
+        <v>2618264</v>
       </c>
     </row>
     <row r="30">
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>3532246</v>
+        <v>3227951</v>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F30" s="18" t="n">
-        <v>1412899</v>
+        <v>1291181</v>
       </c>
     </row>
     <row r="31">
@@ -1015,15 +1015,15 @@
         </is>
       </c>
       <c r="B31" s="20" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D31" s="21" t="n">
-        <v>907168</v>
+        <v>819728</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="F31" s="21" t="n">
-        <v>635018</v>
+        <v>573809</v>
       </c>
     </row>
     <row r="32">
@@ -1041,15 +1041,15 @@
         </is>
       </c>
       <c r="B32" s="21" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D32" s="21" t="n">
-        <v>224699</v>
+        <v>155733</v>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="F32" s="21" t="n">
-        <v>213464</v>
+        <v>147947</v>
       </c>
     </row>
     <row r="33">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B33" s="22" t="n">
-        <v>1159</v>
+        <v>1189</v>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
@@ -1075,11 +1075,11 @@
         </is>
       </c>
       <c r="D33" s="22" t="n">
-        <v>54272664</v>
+        <v>51580059</v>
       </c>
       <c r="E33" s="11" t="inlineStr"/>
       <c r="F33" s="22" t="n">
-        <v>6430943</v>
+        <v>6127278</v>
       </c>
     </row>
     <row r="34">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B39" s="24" t="n">
-        <v>-6309938</v>
+        <v>-6011986</v>
       </c>
       <c r="C39" s="9" t="inlineStr"/>
       <c r="D39" s="9" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="B42" s="24" t="n">
-        <v>-3208954</v>
+        <v>-2911002</v>
       </c>
       <c r="C42" s="9" t="inlineStr"/>
       <c r="D42" s="9" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Que compra el cliente junto con cada producto de rotiseria? | 16/02/2026 - 18/03/2026</t>
+          <t xml:space="preserve">  Que compra el cliente junto con cada producto de rotiseria? | 01/03/2026 - 31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1315,698 +1315,698 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>MATAMBRE NINO</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>140</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>1611958</v>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>8926152</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>5.5x</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>63758</v>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $1,842,930</t>
+      <c r="B6" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1593058</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>7838438</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>4.9x</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>52256</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $1,619,875</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>ENSALADA MIXTA NINO</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>174892</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>7816461</v>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>44.7x</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>76632</v>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $2,748,045</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>EMPANADA CARNE X 6 UN.</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>187</v>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>1457500</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>7440057</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>5.1x</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>39786</v>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $1,657,801</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>ENSALADA MIXTA NINO</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="n">
-        <v>92</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>176288</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>6511127</v>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>36.9x</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>70773</v>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $2,238,773</t>
+      <c r="B8" s="18" t="n">
+        <v>195</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>6819202</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>6.2x</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>34970</v>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $1,579,126</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>EMPANADA J&amp;Q X 6 UN.</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>616000</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>4469313</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>7.3x</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>40630</v>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $1,010,801</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>ENSALADA RUSA NINO</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
-        <v>89</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>192465</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>4713469</v>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>24.5x</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>52960</v>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $1,074,428</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>EMPANADA J&amp;Q X 6 UN.</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>654500</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>4614384</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>7.1x</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>47086</v>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $1,193,384</t>
+      <c r="B10" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>137028</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>3547856</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>25.9x</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>46682</v>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $953,357</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>EMPANADA POLLO X 6 UN.</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>473000</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>3539495</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>7.5x</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>41157</v>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $844,143</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>EMPANADA CARNE X 12 UN.</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n">
+        <v>93</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1661000</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3352829</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>36052</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $851,384</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>LENGUA A LA VINAGRETA NINO</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>56</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>386625</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>3224812</v>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>8.3x</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>57586</v>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $764,192</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>PATITAS ALIÑADAS NINO</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n">
-        <v>65</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>199092</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>3636761</v>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>18.3x</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>55950</v>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $1,050,911</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>LENGUA A LA VINAGRETA NINO</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="n">
-        <v>48</v>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>350745</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>3302456</v>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>9.4x</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>68801</v>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $791,122</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>EMPANADA CARNE X 12 UN.</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="n">
-        <v>80</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>1573000</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>3214753</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>2.0x</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>40184</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $871,250</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>EMPANADA POLLO X 6 UN.</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>561000</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>3066315</v>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>5.5x</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>38329</v>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $651,287</t>
+      <c r="B14" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>195578</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>3031210</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>15.5x</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>41523</v>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $817,167</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>MIGA TRIP. X 6 UNI.</t>
+          <t>EMPANADA VERDURA X 6 UN.</t>
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>248500</v>
+        <v>264000</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>2264251</v>
+        <v>2269711</v>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>9.1x</t>
+          <t>8.6x</t>
         </is>
       </c>
       <c r="F15" s="18" t="n">
-        <v>45285</v>
+        <v>47286</v>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>CARNICERIA AL 10,5 %: $405,192</t>
+          <t>CARNICERIA AL 10,5 %: $495,746</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>TORTILLA DE PAPA NINO</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="n">
-        <v>48</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>192855</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>1986404</v>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>10.3x</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>41383</v>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>ALMACEN: $367,612</t>
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>SALSA BOLOGNESA NINO</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>266570</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>2015681</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>7.6x</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>36649</v>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>ALMACEN: $365,423</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>SALSA BOLOGNESA NINO</t>
+          <t>EMPANADA CAPRESE X 6 UN.</t>
         </is>
       </c>
       <c r="B17" s="27" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>250126</v>
+        <v>231000</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1906694</v>
+        <v>1959466</v>
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>7.6x</t>
+          <t>8.5x</t>
         </is>
       </c>
       <c r="F17" s="18" t="n">
-        <v>36667</v>
+        <v>46654</v>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>ALMACEN: $451,894</t>
+          <t>CARNICERIA AL 10,5 %: $417,191</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>POROTOS ALIÑADOS NINO</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="n">
-        <v>29</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>78815</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>1841242</v>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>23.4x</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>63491</v>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $558,462</t>
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>EMPANADA HUMITA X 6 UN.</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>192500</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1737560</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>9.0x</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>49645</v>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>ALMACEN: $342,813</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>PERNIL DE CERDO HORNEADO NINO</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="n">
-        <v>42</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>422752</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>1801808</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>4.3x</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>42900</v>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $429,517</t>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>EMPANADA CEB/QUEX 6 UN.</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>1699437</v>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>10.3x</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>56648</v>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $493,986</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>EMPANADA HUMITA X 6 UN.</t>
+          <t>MIGA TRIP. X 6 UNI.</t>
         </is>
       </c>
       <c r="B20" s="27" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>225500</v>
+        <v>208740</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1639906</v>
+        <v>1643097</v>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>7.3x</t>
+          <t>7.9x</t>
         </is>
       </c>
       <c r="F20" s="18" t="n">
-        <v>44322</v>
+        <v>39121</v>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>ALMACEN: $298,446</t>
+          <t>CARNICERIA AL 10,5 %: $316,076</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>BERENJENAS EN ESCABECHE NINO</t>
+          <t>TORTILLA DE PAPA NINO</t>
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>98212</v>
+        <v>145977</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1618062</v>
+        <v>1570711</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>16.5x</t>
+          <t>10.8x</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>57788</v>
+        <v>31414</v>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>ALMACEN: $355,566</t>
+          <t>CARNICERIA AL 10,5 %: $360,875</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>EMPANADA VERDURA X 6 UN.</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="n">
-        <v>42</v>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>269500</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>1493472</v>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>5.5x</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>35559</v>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>ALMACEN: $337,619</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>PERNIL DE CERDO HORNEADO NINO</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>339998</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>1424254</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>4.2x</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>41890</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $416,716</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>EMPANADA CEB/QUEX 6 UN.</t>
+          <t>PIZZA MUZZARELLA NINO</t>
         </is>
       </c>
       <c r="B23" s="27" t="n">
         <v>31</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>187000</v>
+        <v>232500</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1412334</v>
+        <v>1229307</v>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>7.6x</t>
+          <t>5.3x</t>
         </is>
       </c>
       <c r="F23" s="18" t="n">
-        <v>45559</v>
+        <v>39655</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>CARNICERIA AL 10,5 %: $382,418</t>
+          <t>ALMACEN: $208,011</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>PIZZA MUZZARELLA NINO</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="n">
-        <v>32</v>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>1351207</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>4.5x</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>42225</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $358,197</t>
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>ARROLLADO DE POLLO NINO</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>127565</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1121183</v>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>8.8x</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>53390</v>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>ALMACEN: $207,135</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>POROTOS ALIÑADOS NINO</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>53680</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>1050824</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>19.6x</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>45688</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $358,676</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>MIGA TRIP. X 12 UNI.</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>302250</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>1292299</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="B26" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>224250</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>971972</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>4.3x</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>47863</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $207,956</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>ARROLLADO DE POLLO NINO</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="n">
-        <v>22</v>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>150505</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>1248082</v>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>8.3x</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>56731</v>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>ALMACEN: $175,119</t>
+      <c r="F26" s="8" t="n">
+        <v>42260</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $180,679</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>PIZZA C/JAMON NINO</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>257400</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>960977</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>3.7x</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>36961</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>ALMACEN: $184,708</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>BERENJENAS EN ESCABECHE NINO</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>82904</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>946849</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>11.4x</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>37874</v>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>ALMACEN: $197,345</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>EMPANADA ATUN X 6 UN.</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>99000</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>1210383</v>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>12.2x</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>80692</v>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $333,953</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>EMPANADA CAPRESE X 6 UN.</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="n">
-        <v>38</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>242000</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>1209482</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>5.0x</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>31828</v>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $199,686</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>PIZZA C/JAMON NINO</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>316800</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>1176809</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>3.7x</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>39227</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>ALMACEN: $222,509</t>
+      <c r="B29" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>96000</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>942845</v>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>9.8x</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>55461</v>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>ALMACEN: $229,378</t>
         </is>
       </c>
     </row>
@@ -2017,199 +2017,199 @@
         </is>
       </c>
       <c r="B30" s="28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>277356</v>
+        <v>243190</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>976424</v>
+        <v>896954</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>3.5x</t>
+          <t>3.7x</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>40684</v>
+        <v>35878</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>CARNICERIA AL 10,5 %: $162,270</t>
+          <t>ALMACEN: $161,706</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>ARROZ CON POLLO</t>
         </is>
       </c>
-      <c r="B31" s="27" t="n">
-        <v>39</v>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>194814</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>974985</v>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>5.0x</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>ALMACEN: $216,498</t>
+      <c r="B31" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>140146</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>535841</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>17861</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>ALMACEN: $118,561</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>EMPANADA J&amp;Q X 12 UN.</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>514051</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>28558</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $92,178</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>CANELONES VERD Y RIC NINO</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>148268</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>476991</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>3.2x</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>29812</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $93,196</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>CUERITOS DE CERDO ALIÑADOS NINO</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>31262</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>466577</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>14.9x</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>25921</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>ALMACEN: $120,906</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>CEBOLLITAS EN ESCABECHE NINO</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>13677</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>709847</v>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>51.9x</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>70985</v>
-      </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $254,395</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="B35" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>7661</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>354188</v>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>46.2x</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>59031</v>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $137,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>CANELONES HUMITA NINO</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>84876</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>497966</v>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>5.9x</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>62246</v>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $172,705</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>CANELONES VERD Y RIC NINO</t>
-        </is>
-      </c>
-      <c r="B34" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>109658</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>496048</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>4.5x</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>41337</v>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $106,478</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>EMPANADA J&amp;Q X 12 UN.</t>
-        </is>
-      </c>
-      <c r="B35" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>220000</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>413323</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>1.9x</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>25833</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>CARNICERIA AL 10,5 %: $82,040</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>CUERITOS DE CERDO ALIÑADOS NINO</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>20801</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>321307</v>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>15.4x</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>26776</v>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>ALMACEN: $84,261</t>
+      <c r="B36" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>67416</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>325556</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>4.8x</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>46508</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>CARNICERIA AL 10,5 %: $120,882</t>
         </is>
       </c>
     </row>
@@ -2220,83 +2220,83 @@
         </is>
       </c>
       <c r="B37" s="27" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>26000</v>
+        <v>12000</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>251060</v>
+        <v>86065</v>
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>9.7x</t>
+          <t>7.2x</t>
         </is>
       </c>
       <c r="F37" s="18" t="n">
-        <v>22824</v>
+        <v>14344</v>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>ALMACEN: $47,031</t>
+          <t>PERFUMERIA: $22,505</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>EMPANADA CARNE X 18 UN.</t>
+          <t>ROTISERIA</t>
         </is>
       </c>
       <c r="B38" s="28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C38" s="8" t="n">
-        <v>99000</v>
+        <v>196460</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>77348</v>
+        <v>62498</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>0.8x</t>
+          <t>0.3x</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>15470</v>
+        <v>8928</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>REPOSTERIA Y PASTELERIA: $38,886</t>
+          <t>LACTEOS: $24,360</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>ROTISERIA</t>
+          <t>EMPANADA CARNE X 18 UN.</t>
         </is>
       </c>
       <c r="B39" s="28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>82003</v>
+        <v>132000</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>67922</v>
+        <v>57747</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>0.8x</t>
+          <t>0.4x</t>
         </is>
       </c>
       <c r="F39" s="8" t="n">
-        <v>13584</v>
+        <v>7218</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>CARNICERIA AL 10,5 %: $22,464</t>
+          <t>REPOSTERIA Y PASTELERIA: $24,954</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Que otros departamentos compra el cliente cuando lleva rotiseria? | 16/02/2026 - 18/03/2026</t>
+          <t xml:space="preserve">  Que otros departamentos compra el cliente cuando lleva rotiseria? | 01/03/2026 - 31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2405,18 +2405,18 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>12400657</v>
+        <v>12387053</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>12167325</v>
+        <v>12153976</v>
       </c>
     </row>
     <row r="7">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>8404333</v>
+        <v>7624766</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>887</v>
+        <v>910</v>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>8246196</v>
+        <v>7481298</v>
       </c>
     </row>
     <row r="8">
@@ -2447,39 +2447,39 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>5495990</v>
+        <v>5216350</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>5392577</v>
+        <v>5118199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>BEBIDAS</t>
+          <t>FIAMBRERIA</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>3634754</v>
+        <v>3358550</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>529</v>
+        <v>478</v>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>3566362</v>
+        <v>3295355</v>
       </c>
     </row>
     <row r="10">
@@ -2489,39 +2489,39 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>3321689</v>
+        <v>3223829</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>3259188</v>
+        <v>3163169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>FIAMBRERIA</t>
+          <t>BEBIDAS</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>3120905</v>
+        <v>3030711</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>3062182</v>
+        <v>2973685</v>
       </c>
     </row>
     <row r="12">
@@ -2531,18 +2531,18 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>3091002</v>
+        <v>2867889</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>3032841</v>
+        <v>2813926</v>
       </c>
     </row>
     <row r="13">
@@ -2552,186 +2552,186 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2393730</v>
+        <v>2238109</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>2348689</v>
+        <v>2195997</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ELABORADOS DE CARNICERIA</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1356643</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>8.4%</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1331116</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>ART.DE 1RA NECESIDAD</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>1348132</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>288</v>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>24.2%</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1322765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>PANAD.ELAB.PROPIA</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>1729924</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>589</v>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>50.8%</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>1697374</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>ELABORADOS DE CARNICERIA</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>1365387</v>
-      </c>
-      <c r="C15" s="28" t="n">
-        <v>92</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>1339696</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>ART.DE 1RA NECESIDAD</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n">
-        <v>1330420</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>248</v>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>21.4%</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>1305387</v>
+      <c r="B16" s="16" t="n">
+        <v>1297189</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>561</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>47.2%</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>1272781</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>PANIFIC.Y MASAS FRESCAS</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>1175955</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>255</v>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>22.0%</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>1153828</v>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>REPOSTERIA Y PASTELERIA</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>1045771</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1026093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
+          <t>PANIFIC.Y MASAS FRESCAS</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>1010150</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>270</v>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>991143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
           <t>GOLOSINAS</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
-        <v>1101392</v>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>256</v>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>22.1%</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>1080668</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>REPOSTERIA Y PASTELERIA</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>1056281</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>10.1%</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>1036406</v>
+      <c r="B19" s="18" t="n">
+        <v>973409</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>251</v>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>955093</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>EMBUTIDOS</t>
+          <t>BAZAR</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1042914</v>
+        <v>920116</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>1023290</v>
+        <v>902803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>BAZAR</t>
+          <t>EMBUTIDOS</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>849456</v>
+        <v>906855</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>833473</v>
+        <v>889791</v>
       </c>
     </row>
     <row r="22">
@@ -2741,18 +2741,18 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>840100</v>
+        <v>702355</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>824293</v>
+        <v>689139</v>
       </c>
     </row>
     <row r="23">
@@ -2762,39 +2762,39 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>497800</v>
+        <v>288290</v>
       </c>
       <c r="C23" s="28" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>488433</v>
+        <v>282865</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>FACTURAS Y TORTITAS</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>177325</v>
-      </c>
-      <c r="C24" s="28" t="n">
-        <v>40</v>
+        <v>247250</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>107</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>173988</v>
+        <v>242598</v>
       </c>
     </row>
     <row r="25">
@@ -2804,81 +2804,81 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>173920</v>
+        <v>232590</v>
       </c>
       <c r="C25" s="28" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>170647</v>
+        <v>228214</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>PESCADOS Y MARISCOS CONGELADOS</t>
+          <t>COTILLON</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>166835</v>
+        <v>199450</v>
       </c>
       <c r="C26" s="28" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>163696</v>
+        <v>195697</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>HUEVOS FRESCOS</t>
+          <t>PASCUA</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>159550</v>
+        <v>198290</v>
       </c>
       <c r="C27" s="28" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>156548</v>
+        <v>194559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>COTILLON</t>
+          <t>PESCADOS Y MARISCOS CONGELADOS</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>155942</v>
+        <v>181130</v>
       </c>
       <c r="C28" s="28" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>153008</v>
+        <v>177721</v>
       </c>
     </row>
     <row r="29">
@@ -2888,238 +2888,238 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>117400</v>
+        <v>137700</v>
       </c>
       <c r="C29" s="28" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
-        <v>115191</v>
+        <v>135109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>HARINAS</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>102835</v>
+        <v>116710</v>
       </c>
       <c r="C30" s="28" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E30" s="8" t="n">
-        <v>100900</v>
+        <v>114514</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>PASCUA</t>
+          <t>HARINAS</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>98960</v>
+        <v>109155</v>
       </c>
       <c r="C31" s="28" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
-        <v>97098</v>
+        <v>107101</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>LEGUMBRES Y CEREALES 10,5% IVA</t>
+          <t>ENVASES VENTA</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>76905</v>
+        <v>92330</v>
       </c>
       <c r="C32" s="28" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>75458</v>
+        <v>90593</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>FERRETERIA</t>
+          <t>HUEVOS FRESCOS</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>67160</v>
+        <v>86950</v>
       </c>
       <c r="C33" s="28" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>65896</v>
+        <v>85314</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>ZAPATERIA</t>
+          <t>LEGUMBRES Y CEREALES 10,5% IVA</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>25600</v>
+        <v>72820</v>
       </c>
       <c r="C34" s="28" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E34" s="8" t="n">
-        <v>25118</v>
+        <v>71450</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>LIBROS DE TEXTOS</t>
+          <t>FERRETERIA</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>23600</v>
+        <v>50975</v>
       </c>
       <c r="C35" s="28" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>23156</v>
+        <v>50016</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>FACTURAS Y TORTITAS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>17450</v>
+        <v>23625</v>
       </c>
       <c r="C36" s="28" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>17122</v>
+        <v>23180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>PRODUCTOS NAVIDEÑOS</t>
+          <t>CONGELADOS AL 10.5%</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>8700</v>
+        <v>18676</v>
       </c>
       <c r="C37" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>8536</v>
+        <v>18325</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>CONGELADOS AL 10.5%</t>
+          <t>PRODUCTOS NAVIDEÑOS</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>8300</v>
+        <v>5460</v>
       </c>
       <c r="C38" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>8144</v>
+        <v>5357</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>PRODUCTOS PARA CARNEO</t>
+          <t>LIBROS DE TEXTOS</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>6600</v>
+        <v>5200</v>
       </c>
       <c r="C39" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>6476</v>
+        <v>5102</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>MEDICAMENTOS</t>
+          <t>IVA RED IB GRAL</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1380</v>
+        <v>1850</v>
       </c>
       <c r="C40" s="28" t="n">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>1354</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>ENVASES VENTA</t>
-        </is>
-      </c>
-      <c r="B41" s="28" t="n">
-        <v>0</v>
+          <t>MEDICAMENTOS</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>1380</v>
       </c>
       <c r="C41" s="28" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E41" s="28" t="n">
-        <v>0</v>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>1354</v>
       </c>
     </row>
     <row r="42">
@@ -3161,12 +3161,12 @@
         </is>
       </c>
       <c r="B42" s="22" t="n">
-        <v>54272664</v>
+        <v>51580059</v>
       </c>
       <c r="C42" s="11" t="inlineStr"/>
       <c r="D42" s="11" t="inlineStr"/>
       <c r="E42" s="22" t="n">
-        <v>53251462</v>
+        <v>50609522</v>
       </c>
     </row>
     <row r="44">
@@ -3230,7 +3230,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Seba: 'Hay parte de la produccion de panaderia que corresponde a rotiseria?' | 16/02/2026 - 18/03/2026</t>
+          <t xml:space="preserve">  Seba: 'Hay parte de la produccion de panaderia que corresponde a rotiseria?' | 01/03/2026 - 31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>4.6% de tickets tiene rotis</t>
+          <t>4.7% de tickets tiene rotis</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>39.9% de tickets tiene panaderia</t>
+          <t>37.1% de tickets tiene panaderia</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>588 tickets con ambos</t>
+          <t>561 tickets con ambos</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>vs 39.9% promedio → +27%</t>
+          <t>vs 37.1% promedio → +27%</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt;&gt; 50.8% de los que compran rotis TAMBIEN compran panaderia (vs 39.9% general)</t>
+          <t xml:space="preserve">  &gt;&gt;&gt; 47.2% de los que compran rotis TAMBIEN compran panaderia (vs 37.1% general)</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>vs 4.6% promedio → +27%</t>
+          <t>vs 4.7% promedio → +27%</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt;&gt; 5.9% de los que compran panaderia TAMBIEN compran rotis (vs 4.6% general)</t>
+          <t xml:space="preserve">  &gt;&gt;&gt; 6.0% de los que compran panaderia TAMBIEN compran rotis (vs 4.7% general)</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3430,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>p-value = 1.25e-14 (***)</t>
+          <t>p-value = 1.95e-13 (***)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>0.0488</t>
+          <t>0.0464</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Asociacion estadisticamente significativa (p&lt;0.001) pero DEBIL en magnitud (V=0.049)</t>
+          <t xml:space="preserve">  Asociacion estadisticamente significativa (p&lt;0.001) pero DEBIL en magnitud (V=0.046)</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>28222420</v>
+        <v>20896544</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>27691383</v>
+        <v>20503352</v>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr"/>
@@ -3527,15 +3527,15 @@
         </is>
       </c>
       <c r="B26" s="29" t="n">
-        <v>1728264</v>
+        <v>1297189</v>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="D26" s="29" t="n">
-        <v>1695744</v>
+        <v>1272781</v>
       </c>
       <c r="E26" s="14" t="inlineStr"/>
       <c r="F26" s="14" t="inlineStr"/>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="B27" s="31" t="n">
-        <v>864132</v>
+        <v>648594</v>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>847872</v>
+        <v>636390</v>
       </c>
       <c r="E27" s="30" t="inlineStr"/>
       <c r="F27" s="30" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>11369307</v>
+        <v>10575200</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>11155381</v>
+        <v>10376216</v>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="7" t="inlineStr"/>
@@ -3591,15 +3591,15 @@
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>5594672</v>
+        <v>4817212</v>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="D30" s="29" t="n">
-        <v>5489402</v>
+        <v>4726571</v>
       </c>
       <c r="E30" s="14" t="inlineStr"/>
       <c r="F30" s="14" t="inlineStr"/>
@@ -3635,7 +3635,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - La 'produccion de panaderia que corresponde a rotiseria' es ~$847,872/mes (3% de panad)</t>
+          <t xml:space="preserve">  - La 'produccion de panaderia que corresponde a rotiseria' es ~$636,390/mes (3% de panad)</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3703,7 +3703,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Lift, Chi-squared y Cramer's V para cada departamento | 16/02/2026 - 18/03/2026</t>
+          <t xml:space="preserve">  Lift, Chi-squared y Cramer's V para cada departamento | 01/03/2026 - 31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3759,17 +3759,17 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>0.0294</t>
+          <t>0.0317</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -3791,22 +3791,22 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>REPOSTERIA Y PASTELERIA</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>0.0878</t>
+          <t>0.0394</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -3828,22 +3828,22 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>REPOSTERIA Y PASTELERIA</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>0.0270</t>
+          <t>0.0812</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>EMBUTIDOS</t>
+          <t>PASCUA</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>0.0478</t>
+          <t>0.0246</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>LIBROS DE TEXTOS</t>
+          <t>PRODUCTOS NAVIDEÑOS</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0082</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -3939,22 +3939,22 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>CONGELADOS HELADOS</t>
+          <t>EMBUTIDOS</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>0.0332</t>
+          <t>0.0481</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -3976,32 +3976,32 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>PASCUA</t>
+          <t>TEXTIL</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>**</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0180</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -4013,22 +4013,22 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>FIAMBRERIA</t>
+          <t>CONGELADOS HELADOS</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>0.0727</t>
+          <t>0.0222</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -4050,32 +4050,32 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>PRODUCTOS NAVIDEÑOS</t>
+          <t>ENVASES VENTA</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>**</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>0.0055</t>
+          <t>0.0189</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -4092,138 +4092,138 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>0.0286</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>FUERTE arrastre</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>FIAMBRERIA</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>26.1%</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>40.2%</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>0.0709</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>FUERTE arrastre</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>PANIFIC.Y MASAS FRESCAS</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>22.6%</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>0.0263</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>0.0474</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>FUERTE arrastre</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>PANIFIC.Y MASAS FRESCAS</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>14.8%</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>22.0%</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>0.0446</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>Arrastre moderado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>BEBIDAS</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>31.1%</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>45.7%</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>0.0695</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>Arrastre moderado</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>LACTEOS</t>
+          <t>FERRETERIA</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>0.0692</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -4235,32 +4235,32 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>PRODUCTOS PARA CARNEO</t>
+          <t>LACTEOS</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>***</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0714</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
@@ -4272,32 +4272,32 @@
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>COTILLON</t>
+          <t>BEBIDAS</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>***</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>0.0102</t>
+          <t>0.0577</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
@@ -4309,32 +4309,32 @@
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>GOLOSINAS</t>
+          <t>LIBROS DE TEXTOS</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0002</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
@@ -4346,32 +4346,32 @@
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>PANAD.ELAB.PROPIA</t>
+          <t>COTILLON</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>0.0488</t>
+          <t>0.0104</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -4383,32 +4383,32 @@
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>LECHES</t>
+          <t>PANAD.ELAB.PROPIA</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>***</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>0.0176</t>
+          <t>0.0464</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
@@ -4420,32 +4420,32 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>HUEVOS FRESCOS</t>
+          <t>GOLOSINAS</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>***</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>0.0111</t>
+          <t>0.0257</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -4457,22 +4457,22 @@
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>TEXTIL</t>
+          <t>CONGELADOS AL 10.5%</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>0.0039</t>
+          <t>0.0017</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
@@ -4492,135 +4492,135 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>PERFUMERIA</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>32.8%</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>0.0236</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Independiente</t>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>BAZAR</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>0.0187</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Arrastre moderado</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>LIMPIEZA</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>30.6%</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>35.5%</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>0.0235</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Independiente</t>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>LECHES</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>13.4%</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>0.0189</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Arrastre moderado</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>BAZAR</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>10.3%</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>HUEVOS FRESCOS</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>0.0103</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Independiente</t>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Arrastre moderado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>ALMACEN</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>0.0333</t>
+          <t>0.0277</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -4642,32 +4642,32 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>POLLO</t>
+          <t>CARNICERIA AL 10,5 %</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>**</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0193</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -4679,32 +4679,32 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>CARNICERIA AL 10,5 %</t>
+          <t>PERFUMERIA</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>**</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>0.0099</t>
+          <t>0.0188</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -4716,22 +4716,22 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>LEGUMBRES Y CEREALES 10,5% IVA</t>
+          <t>POLLO</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -4753,22 +4753,22 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>ART.DE 1RA NECESIDAD</t>
+          <t>FACTURAS Y TORTITAS</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>0.0052</t>
+          <t>0.0079</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -4790,32 +4790,32 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>ZAPATERIA</t>
+          <t>ALMACEN</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>***</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0324</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -4827,22 +4827,22 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>FERRETERIA</t>
+          <t>ART.DE 1RA NECESIDAD</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0110</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -4864,170 +4864,170 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>IVA RED IB GRAL</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>LEGUMBRES Y CEREALES 10,5% IVA</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>MEDICAMENTOS</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
           <t>LIBRERIA</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>0.0036</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>Independiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>HARINAS</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>0.0047</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="inlineStr">
-        <is>
-          <t>Relacion inversa</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>FACTURAS Y TORTITAS</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>0.0023</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>Relacion inversa</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>MEDICAMENTOS</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>Relacion inversa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>CONGELADOS AL 10.5%</t>
+          <t>HARINAS</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>0.0079</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="G40" s="19" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>0.0026</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="G41" s="19" t="inlineStr">
@@ -5086,63 +5086,137 @@
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>ENVASES VENTA</t>
+          <t>HELADOS</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>0.0013</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>Relacion inversa</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>PRODUCTOS PARA CARNEO</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D42" s="19" t="inlineStr">
+      <c r="D43" s="19" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>0.0005</t>
-        </is>
-      </c>
-      <c r="G42" s="19" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
         <is>
           <t>Relacion inversa</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Verde = Lift &gt; 1.5 (fuerte asociacion) | Amarillo = 1.2-1.5 (moderada) | Sin color = independiente | Rojo = inversa</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Lift &gt; 1: se compra MAS cuando hay rotis. Lift = 1: independiente. Lift &lt; 1: se compra MENOS.</t>
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>ZAPATERIA</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>Relacion inversa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *** p&lt;0.001 | ** p&lt;0.01 | * p&lt;0.05 | ns = no significativo</t>
+          <t xml:space="preserve">  Verde = Lift &gt; 1.5 (fuerte asociacion) | Amarillo = 1.2-1.5 (moderada) | Sin color = independiente | Rojo = inversa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Lift &gt; 1: se compra MAS cuando hay rotis. Lift = 1: independiente. Lift &lt; 1: se compra MENOS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  *** p&lt;0.001 | ** p&lt;0.01 | * p&lt;0.05 | ns = no significativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Metodo: Association Rules (Market Basket Analysis) + Chi-Squared test de independencia</t>
         </is>
@@ -5151,11 +5225,11 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
